--- a/Hoadon/HDVao/9/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/9/HDDienTuKhongMa.xlsx
@@ -314,6 +314,164 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>K25THA</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>1120564</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>0106869738-044</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+        </is>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Cổ Phần Đầu Tư Xây Dựng Thương Mại Dịch Vụ Kỹ Thuật H Và V</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>432894.0</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>43289.0</v>
+      </c>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>476183.0</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>K25TVT</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>5989806</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0310471746-364</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CN CÔNG TY CP THƯƠNG MẠI BÁCH HÓA XANH - CH BÁCH HÓA XANH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Số 290 Trương Công Định, Phường Tam Thắng, Thành Phố Hồ Chí Minh. Việt Nam</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>429678.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>24928.0</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>454606.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDVao/9/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/9/HDDienTuKhongMa.xlsx
@@ -314,164 +314,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>K25THA</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>1120564</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>01/09/2025</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>0106869738-044</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
-        </is>
-      </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty Cổ Phần Đầu Tư Xây Dựng Thương Mại Dịch Vụ Kỹ Thuật H Và V</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>432894.0</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>43289.0</v>
-      </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13" t="n">
-        <v>476183.0</v>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>K25TVT</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>5989806</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>17/09/2025</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>0310471746-364</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>CN CÔNG TY CP THƯƠNG MẠI BÁCH HÓA XANH - CH BÁCH HÓA XANH BÀ RỊA VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Số 290 Trương Công Định, Phường Tam Thắng, Thành Phố Hồ Chí Minh. Việt Nam</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="n">
-        <v>429678.0</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>24928.0</v>
-      </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13" t="n">
-        <v>454606.0</v>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn điều chỉnh</t>
-        </is>
-      </c>
-      <c r="S8" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDVao/9/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/9/HDDienTuKhongMa.xlsx
@@ -325,50 +325,50 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25THA</t>
+          <t>K25TVA</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1120564</t>
+          <t>2475910</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>04/09/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0106869738-044</t>
+          <t>0100109106-122</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+          <t>Viettel Hồ Chí Minh- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Cổ Phần Đầu Tư Xây Dựng Thương Mại Dịch Vụ Kỹ Thuật H Và V</t>
+          <t>Công Ty Tnhh Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>432894.0</v>
+        <v>0.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>43289.0</v>
+        <v>0.0</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>476183.0</v>
+        <v>0.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -402,71 +402,1337 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>K25TVT</t>
+          <t>K25TAA</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>5989806</t>
+          <t>27558</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>17/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0310471746-364</t>
+          <t>0100150619-006</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CN CÔNG TY CP THƯƠNG MẠI BÁCH HÓA XANH - CH BÁCH HÓA XANH BÀ RỊA VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Số 290 Trương Công Định, Phường Tam Thắng, Thành Phố Hồ Chí Minh. Việt Nam</t>
-        </is>
-      </c>
+          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Bà Rịa - Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H8" s="6"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CTY TNHH DAI LY TAU BIEN VUNG TAU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>429678.0</v>
+        <v>96.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>24928.0</v>
+        <v>9.6</v>
       </c>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>454606.0</v>
+        <v>105.6</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>26340.5</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>K25TAA</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>28347</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>0100150619-006</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Bà Rịa - Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DAI LY TAU BIEN VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>120000.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>12000.0</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>132000.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="Q8" s="7" t="inlineStr">
+      <c r="Q9" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn điều chỉnh</t>
-        </is>
-      </c>
-      <c r="S8" s="6" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>K25DAA</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>458370</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>07/09/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0100686209-129</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+        </is>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>334682.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>33468.0</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>368150.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>K25DAA</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>478974</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>07/09/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>0100686209-129</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+        </is>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>136364.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>13636.0</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>150000.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>K25DAA</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>499227</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>07/09/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>0100686209-129</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+        </is>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>178309.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>17831.0</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>196140.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K25DAA</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>499417</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>07/09/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>0100686209-129</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+        </is>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>151818.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>15182.0</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>167000.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>K25TAN</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>888725</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>0104093672</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>TỔNG CÔNG TY CP BƯU CHÍNH VIETTEL</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Số 2, ngõ 15 phố Duy Tân, Phường Cầu Giấy, Thành Phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>83333.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>6667.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>90000.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>K25THA</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>1103659</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>0106869738-044</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+        </is>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>117001.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>11700.0</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>128701.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>1087784</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>1371120.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>109690.0</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>1480810.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>407529</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3500102573</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BÀ RỊA -VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Hoàng Hoa Thám - Phường Vũng Tàu - TP Hồ Chí Minh - Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>412130</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>07/09/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3500102573</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BÀ RỊA -VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Hoàng Hoa Thám - Phường Vũng Tàu - TP Hồ Chí Minh - Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>419342</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3500102573</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BÀ RỊA -VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Hoàng Hoa Thám - Phường Vũng Tàu - TP Hồ Chí Minh - Việt Nam</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>583333.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>46667.0</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>630000.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>423564</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3500102573</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BÀ RỊA -VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Hoàng Hoa Thám - Phường Vũng Tàu - TP Hồ Chí Minh - Việt Nam</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>736289.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>58903.0</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>795192.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>432670</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3500102573</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BÀ RỊA -VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Hoàng Hoa Thám - Phường Vũng Tàu - TP Hồ Chí Minh - Việt Nam</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>436561</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>21/09/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3500102573</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BÀ RỊA -VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Hoàng Hoa Thám - Phường Vũng Tàu - TP Hồ Chí Minh - Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>555647.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>44452.0</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>600099.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>447699</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>28/09/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3500102573</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BÀ RỊA -VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Hoàng Hoa Thám - Phường Vũng Tàu - TP Hồ Chí Minh - Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>555561.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>44445.0</v>
+      </c>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>600006.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>450342</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3500102573</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BÀ RỊA -VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Hoàng Hoa Thám - Phường Vũng Tàu - TP Hồ Chí Minh - Việt Nam</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>466667.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>37333.0</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>504000.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>

--- a/Hoadon/HDVao/9/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/9/HDDienTuKhongMa.xlsx
@@ -325,50 +325,50 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25TAA</t>
+          <t>K25TCA</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>36032</t>
+          <t>437868</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0100150619-104</t>
+          <t>0100686174-034</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Phú Mỹ</t>
+          <t>NGÂN HÀNG NÔNG NGHIỆP VÀ PHÁT TRIỂN NÔNG THÔN VIỆT NAM - CHI NHÁNH VŨNG TÀU</t>
         </is>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3500826826</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CTY TNHH NGUYEN KHANG</t>
+          <t>Cty TNHH XD Ngọc Trân</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>130000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>13000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>143000.0</v>
+        <v>55000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -402,56 +402,50 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>K25TPP</t>
+          <t>K25TCA</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>238332</t>
+          <t>482207</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>23/09/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3601038204-075</t>
+          <t>0100686174-034</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN XĂNG DẦU TÍN NGHĨA - TRẠM XĂNG DẦU THÀNH NGHĨA</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Khu phố Tân Hạnh, Phường Phú Mỹ, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG NÔNG NGHIỆP VÀ PHÁT TRIỂN NÔNG THÔN VIỆT NAM - CHI NHÁNH VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H8" s="6"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3500826826</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NGUYÊN KHANG</t>
+          <t>Cty TNHH XD Ngọc Trân</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>1388889.0</v>
+        <v>15000.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>111111.0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>1500.0</v>
+      </c>
+      <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>1500000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -485,56 +479,50 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>K25TPP</t>
+          <t>K25TCA</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>253993</t>
+          <t>489750</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>27/09/2025</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3601038204-075</t>
+          <t>0100686174-034</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN XĂNG DẦU TÍN NGHĨA - TRẠM XĂNG DẦU THÀNH NGHĨA</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Khu phố Tân Hạnh, Phường Phú Mỹ, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG NÔNG NGHIỆP VÀ PHÁT TRIỂN NÔNG THÔN VIỆT NAM - CHI NHÁNH VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H9" s="6"/>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3500826826</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NGUYÊN KHANG</t>
+          <t>Cty TNHH XD Ngọc Trân</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>740870.0</v>
+        <v>20000.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>59270.0</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>2000.0</v>
+      </c>
+      <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>800140.0</v>
+        <v>22000.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -552,6 +540,3071 @@
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>1070767</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>1649210.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>131937.0</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>1781147.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>K25TBC</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>263558</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>06/09/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>423414</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>425689</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>06/09/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>425691</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>06/09/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>429441</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>509259.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>40741.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>550000.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>429557</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>509259.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>40741.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>550000.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>430028</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>430029</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>430749</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>432948</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>537037.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>42963.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>580000.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>432949</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>481723.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>38538.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>520261.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>433593</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>433594</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>92593.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>7407.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>433595</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>436114</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>648148.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>51852.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>700000.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>436117</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>436362</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>833333.0</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>66667.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>436842</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>13/09/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>509259.0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>40741.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>550000.0</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>440231</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>1388889.0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>111111.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="n">
+        <v>1500000.0</v>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>441957</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>416667.0</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>33333.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13" t="n">
+        <v>450000.0</v>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>441958</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>416667.0</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>33333.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="n">
+        <v>450000.0</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>442863</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>601852.0</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>48148.0</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="n">
+        <v>650000.0</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>443467</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>445085</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>448373</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>448662</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>416720.0</v>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>33338.0</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13" t="n">
+        <v>450058.0</v>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>451743</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>451744</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L38" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>452427</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>452449</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="n">
+        <v>648264.0</v>
+      </c>
+      <c r="L40" s="13" t="n">
+        <v>51861.0</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13" t="n">
+        <v>700125.0</v>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>453323</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>23/09/2025</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>1388889.0</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>111111.0</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13" t="n">
+        <v>1500000.0</v>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>454970</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>24/09/2025</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L42" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q42" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>455906</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>24/09/2025</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>555556.0</v>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>44444.0</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>459140</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L44" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q44" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>461225</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>28/09/2025</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>555556.0</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>44444.0</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N45" s="13"/>
+      <c r="O45" s="13" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>K25TLK</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>464514</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="n">
+        <v>463463.0</v>
+      </c>
+      <c r="L46" s="13" t="n">
+        <v>37077.0</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13" t="n">
+        <v>500540.0</v>
+      </c>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q46" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S46" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>

--- a/Hoadon/HDVao/9/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/9/HDDienTuKhongMa.xlsx
@@ -325,50 +325,50 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25TCA</t>
+          <t>K25DAB</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>437868</t>
+          <t>76563360</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0100686174-034</t>
+          <t>0100109106</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>NGÂN HÀNG NÔNG NGHIỆP VÀ PHÁT TRIỂN NÔNG THÔN VIỆT NAM - CHI NHÁNH VŨNG TÀU</t>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Cty TNHH XD Ngọc Trân</t>
+          <t>Cty TNHH Đại Phú Hiệp</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>50000.0</v>
+        <v>578.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>5000.0</v>
+        <v>58.0</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>55000.0</v>
+        <v>636.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -402,50 +402,52 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>K25TCA</t>
+          <t>K25TEA</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>482207</t>
+          <t>600471</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>23/09/2025</t>
+          <t>06/09/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0100686174-034</t>
+          <t>0100112437-005</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>NGÂN HÀNG NÔNG NGHIỆP VÀ PHÁT TRIỂN NÔNG THÔN VIỆT NAM - CHI NHÁNH VŨNG TÀU</t>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
         </is>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Cty TNHH XD Ngọc Trân</t>
+          <t>CT TNHH DAI PHU HIEP</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>15000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>1500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
+      <c r="N8" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O8" s="13" t="n">
-        <v>16500.0</v>
+        <v>55000.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -479,50 +481,52 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>K25TCA</t>
+          <t>K25TEA</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>489750</t>
+          <t>693219</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0100686174-034</t>
+          <t>0100112437-005</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>NGÂN HÀNG NÔNG NGHIỆP VÀ PHÁT TRIỂN NÔNG THÔN VIỆT NAM - CHI NHÁNH VŨNG TÀU</t>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
         </is>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Cty TNHH XD Ngọc Trân</t>
+          <t>CT TNHH DAI PHU HIEP</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>20000.0</v>
+        <v>1926375.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>2000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
+      <c r="N9" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O9" s="13" t="n">
-        <v>22000.0</v>
+        <v>1926375.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -556,50 +560,52 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>K25TDA</t>
+          <t>K25TEA</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1070767</t>
+          <t>697296</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0300951119-010</t>
+          <t>0100112437-005</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
         </is>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CT TNHH DAI PHU HIEP</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1649210.0</v>
+        <v>20000.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>131937.0</v>
+        <v>2000.0</v>
       </c>
       <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O10" s="13" t="n">
-        <v>1781147.0</v>
+        <v>22000.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -633,56 +639,52 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>K25TBC</t>
+          <t>K25TEA</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>263558</t>
+          <t>699027</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>06/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0100112437-005</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+        </is>
+      </c>
+      <c r="H11" s="6"/>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CT TNHH DAI PHU HIEP</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>462963.0</v>
+        <v>1380797.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="N11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O11" s="13" t="n">
-        <v>500000.0</v>
+        <v>1380797.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -716,56 +718,52 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TEA</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>423414</t>
+          <t>699696</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>05/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0100112437-005</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+        </is>
+      </c>
+      <c r="H12" s="6"/>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CT TNHH DAI PHU HIEP</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>462963.0</v>
+        <v>3643831.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="N12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O12" s="13" t="n">
-        <v>500000.0</v>
+        <v>3643831.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -799,56 +797,52 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TEA</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>425689</t>
+          <t>701465</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>06/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0100112437-005</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+        </is>
+      </c>
+      <c r="H13" s="6"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CT TNHH DAI PHU HIEP</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>925926.0</v>
+        <v>58800.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>74074.0</v>
-      </c>
-      <c r="M13" s="13" t="n">
+        <v>5880.0</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>1000000.0</v>
+        <v>64680.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -882,56 +876,52 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TEA</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>425691</t>
+          <t>717665</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>06/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0100112437-005</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+        </is>
+      </c>
+      <c r="H14" s="6"/>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CT TNHH DAI PHU HIEP</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>462963.0</v>
+        <v>20000.0</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M14" s="13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>500000.0</v>
+        <v>22000.0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -965,56 +955,50 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25DGD</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>429441</t>
+          <t>547346</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>08/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0100230800</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>Ngân hàng TMCP Kỹ thương Việt Nam</t>
+        </is>
+      </c>
+      <c r="H15" s="6"/>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CONG TY TNHH DAI PHU HIEP .</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>509259.0</v>
+        <v>200000.0</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>40741.0</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>20000.0</v>
+      </c>
+      <c r="M15" s="13"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>550000.0</v>
+        <v>220000.0</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -1048,62 +1032,52 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TET</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>429557</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>08/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0105402531-017</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>CÔNG TY BẢO HIỂM PVI VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H16" s="6"/>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K16" s="13" t="n">
-        <v>509259.0</v>
+        <v>1540000.0</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>40741.0</v>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>154000.0</v>
+      </c>
+      <c r="M16" s="13"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="n">
-        <v>550000.0</v>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
+        <v>1694000.0</v>
+      </c>
+      <c r="P16" s="7"/>
       <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -1131,56 +1105,50 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25THA</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>430028</t>
+          <t>1102425</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0106869738-044</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+        </is>
+      </c>
+      <c r="H17" s="6"/>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>Công ty TNHH Đại Phú Hiệp</t>
         </is>
       </c>
       <c r="K17" s="13" t="n">
-        <v>462963.0</v>
+        <v>255223.0</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>25522.0</v>
+      </c>
+      <c r="M17" s="13"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="n">
-        <v>500000.0</v>
+        <v>280745.0</v>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
@@ -1214,56 +1182,50 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25THA</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>430029</t>
+          <t>1109112</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0106869738-044</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+        </is>
+      </c>
+      <c r="H18" s="6"/>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>Công Ty TNHH Đại Phú Hiệp</t>
         </is>
       </c>
       <c r="K18" s="13" t="n">
-        <v>462963.0</v>
+        <v>158306.0</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>15831.0</v>
+      </c>
+      <c r="M18" s="13"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13" t="n">
-        <v>500000.0</v>
+        <v>174137.0</v>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
@@ -1297,56 +1259,50 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TBA</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>430749</t>
+          <t>95137</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0300608092</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGAN HANG TMCP PHAT TRIEN THANH PHO HO CHI MINH</t>
+        </is>
+      </c>
+      <c r="H19" s="6"/>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CONG TY TNHH DAI PHU HIEP</t>
         </is>
       </c>
       <c r="K19" s="13" t="n">
-        <v>462963.0</v>
+        <v>4.5112536E7</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M19" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M19" s="13"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13" t="n">
-        <v>500000.0</v>
+        <v>4.5112536E7</v>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
@@ -1380,56 +1336,50 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TBA</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>432948</t>
+          <t>95138</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0300608092</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGAN HANG TMCP PHAT TRIEN THANH PHO HO CHI MINH</t>
+        </is>
+      </c>
+      <c r="H20" s="6"/>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CONG TY TNHH DAI PHU HIEP</t>
         </is>
       </c>
       <c r="K20" s="13" t="n">
-        <v>537037.0</v>
+        <v>120000.0</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>42963.0</v>
-      </c>
-      <c r="M20" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>12000.0</v>
+      </c>
+      <c r="M20" s="13"/>
       <c r="N20" s="13"/>
       <c r="O20" s="13" t="n">
-        <v>580000.0</v>
+        <v>132000.0</v>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
@@ -1463,56 +1413,50 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TDA</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>432949</t>
+          <t>1018706</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>03/09/2025</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0300951119-010</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H21" s="6"/>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>Cty TNHH Đại Phú Hiệp</t>
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>481723.0</v>
+        <v>3786957.0</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>38538.0</v>
-      </c>
-      <c r="M21" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>302957.0</v>
+      </c>
+      <c r="M21" s="13"/>
       <c r="N21" s="13"/>
       <c r="O21" s="13" t="n">
-        <v>520261.0</v>
+        <v>4089914.0</v>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
@@ -1546,56 +1490,50 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TDA</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>433593</t>
+          <t>1040001</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>11/09/2025</t>
+          <t>03/09/2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0300951119-010</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K22" s="13" t="n">
-        <v>925926.0</v>
+        <v>804735.0</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>74074.0</v>
-      </c>
-      <c r="M22" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>64379.0</v>
+      </c>
+      <c r="M22" s="13"/>
       <c r="N22" s="13"/>
       <c r="O22" s="13" t="n">
-        <v>1000000.0</v>
+        <v>869114.0</v>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
@@ -1629,56 +1567,50 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TDA</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>433594</t>
+          <t>1131367</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>11/09/2025</t>
+          <t>03/09/2025</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0300951119-010</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H23" s="6"/>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>92593.0</v>
+        <v>1247836.0</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>7407.0</v>
-      </c>
-      <c r="M23" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>99827.0</v>
+      </c>
+      <c r="M23" s="13"/>
       <c r="N23" s="13"/>
       <c r="O23" s="13" t="n">
-        <v>100000.0</v>
+        <v>1347663.0</v>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
@@ -1712,56 +1644,50 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TTA</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>433595</t>
+          <t>1037376</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>11/09/2025</t>
+          <t>02/09/2025</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0300951119-020</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC ĐẤT ĐỎ</t>
+        </is>
+      </c>
+      <c r="H24" s="6"/>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>Công Ty TNHH Đại Phú Hiệp</t>
         </is>
       </c>
       <c r="K24" s="13" t="n">
-        <v>462963.0</v>
+        <v>363621.0</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M24" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>29090.0</v>
+      </c>
+      <c r="M24" s="13"/>
       <c r="N24" s="13"/>
       <c r="O24" s="13" t="n">
-        <v>500000.0</v>
+        <v>392711.0</v>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
@@ -1795,56 +1721,50 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>436114</t>
+          <t>31530</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>12/09/2025</t>
+          <t>08/09/2025</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H25" s="6"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K25" s="13" t="n">
-        <v>648148.0</v>
+        <v>1.5194E7</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>51852.0</v>
-      </c>
-      <c r="M25" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M25" s="13"/>
       <c r="N25" s="13"/>
       <c r="O25" s="13" t="n">
-        <v>700000.0</v>
+        <v>1.5194E7</v>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
@@ -1878,56 +1798,50 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>436117</t>
+          <t>31632</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>12/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H26" s="6"/>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K26" s="13" t="n">
-        <v>462963.0</v>
+        <v>5182000.0</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M26" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M26" s="13"/>
       <c r="N26" s="13"/>
       <c r="O26" s="13" t="n">
-        <v>500000.0</v>
+        <v>5182000.0</v>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
@@ -1961,56 +1875,50 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>436362</t>
+          <t>31633</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>12/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H27" s="6"/>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K27" s="13" t="n">
-        <v>833333.0</v>
+        <v>4989000.0</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>66667.0</v>
-      </c>
-      <c r="M27" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M27" s="13"/>
       <c r="N27" s="13"/>
       <c r="O27" s="13" t="n">
-        <v>900000.0</v>
+        <v>4989000.0</v>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
@@ -2044,56 +1952,50 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>436842</t>
+          <t>32800</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>13/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H28" s="6"/>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K28" s="13" t="n">
-        <v>509259.0</v>
+        <v>269589.0</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>40741.0</v>
-      </c>
-      <c r="M28" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M28" s="13"/>
       <c r="N28" s="13"/>
       <c r="O28" s="13" t="n">
-        <v>550000.0</v>
+        <v>269589.0</v>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
@@ -2127,56 +2029,50 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>440231</t>
+          <t>32804</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H29" s="6"/>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K29" s="13" t="n">
-        <v>1388889.0</v>
+        <v>1285052.0</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>111111.0</v>
-      </c>
-      <c r="M29" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M29" s="13"/>
       <c r="N29" s="13"/>
       <c r="O29" s="13" t="n">
-        <v>1500000.0</v>
+        <v>1285052.0</v>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
@@ -2210,56 +2106,50 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>441957</t>
+          <t>33060</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H30" s="6"/>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K30" s="13" t="n">
-        <v>416667.0</v>
+        <v>364402.0</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>33333.0</v>
-      </c>
-      <c r="M30" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M30" s="13"/>
       <c r="N30" s="13"/>
       <c r="O30" s="13" t="n">
-        <v>450000.0</v>
+        <v>364402.0</v>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
@@ -2293,56 +2183,50 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>441958</t>
+          <t>33135</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H31" s="6"/>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K31" s="13" t="n">
-        <v>416667.0</v>
+        <v>5616438.0</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>33333.0</v>
-      </c>
-      <c r="M31" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M31" s="13"/>
       <c r="N31" s="13"/>
       <c r="O31" s="13" t="n">
-        <v>450000.0</v>
+        <v>5616438.0</v>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
@@ -2376,56 +2260,50 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>442863</t>
+          <t>33161</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H32" s="6"/>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K32" s="13" t="n">
-        <v>601852.0</v>
+        <v>1347945.0</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>48148.0</v>
-      </c>
-      <c r="M32" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M32" s="13"/>
       <c r="N32" s="13"/>
       <c r="O32" s="13" t="n">
-        <v>650000.0</v>
+        <v>1347945.0</v>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
@@ -2459,56 +2337,50 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>443467</t>
+          <t>33167</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>17/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H33" s="6"/>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K33" s="13" t="n">
-        <v>462963.0</v>
+        <v>1347945.0</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M33" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M33" s="13"/>
       <c r="N33" s="13"/>
       <c r="O33" s="13" t="n">
-        <v>500000.0</v>
+        <v>1347945.0</v>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
@@ -2542,56 +2414,50 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>445085</t>
+          <t>33176</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>18/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H34" s="6"/>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K34" s="13" t="n">
-        <v>462963.0</v>
+        <v>5616438.0</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M34" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M34" s="13"/>
       <c r="N34" s="13"/>
       <c r="O34" s="13" t="n">
-        <v>500000.0</v>
+        <v>5616438.0</v>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
@@ -2625,56 +2491,50 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>448373</t>
+          <t>33241</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>20/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H35" s="6"/>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K35" s="13" t="n">
-        <v>462963.0</v>
+        <v>948504.0</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M35" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M35" s="13"/>
       <c r="N35" s="13"/>
       <c r="O35" s="13" t="n">
-        <v>500000.0</v>
+        <v>948504.0</v>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
@@ -2708,56 +2568,50 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>448662</t>
+          <t>33245</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>20/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H36" s="6"/>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K36" s="13" t="n">
-        <v>416720.0</v>
+        <v>227641.0</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>33338.0</v>
-      </c>
-      <c r="M36" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M36" s="13"/>
       <c r="N36" s="13"/>
       <c r="O36" s="13" t="n">
-        <v>450058.0</v>
+        <v>227641.0</v>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
@@ -2791,56 +2645,50 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>451743</t>
+          <t>33340</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>22/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H37" s="6"/>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K37" s="13" t="n">
-        <v>925926.0</v>
+        <v>404384.0</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>74074.0</v>
-      </c>
-      <c r="M37" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M37" s="13"/>
       <c r="N37" s="13"/>
       <c r="O37" s="13" t="n">
-        <v>1000000.0</v>
+        <v>404384.0</v>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
@@ -2874,56 +2722,50 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>451744</t>
+          <t>33383</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>22/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H38" s="6"/>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K38" s="13" t="n">
-        <v>462963.0</v>
+        <v>5354384.0</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M38" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M38" s="13"/>
       <c r="N38" s="13"/>
       <c r="O38" s="13" t="n">
-        <v>500000.0</v>
+        <v>5354384.0</v>
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
@@ -2957,56 +2799,50 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>452427</t>
+          <t>33401</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>22/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H39" s="6"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K39" s="13" t="n">
-        <v>462963.0</v>
+        <v>1518343.0</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M39" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M39" s="13"/>
       <c r="N39" s="13"/>
       <c r="O39" s="13" t="n">
-        <v>500000.0</v>
+        <v>1518343.0</v>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
@@ -3040,56 +2876,50 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>452449</t>
+          <t>33402</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>22/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H40" s="6"/>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K40" s="13" t="n">
-        <v>648264.0</v>
+        <v>1123288.0</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>51861.0</v>
-      </c>
-      <c r="M40" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M40" s="13"/>
       <c r="N40" s="13"/>
       <c r="O40" s="13" t="n">
-        <v>700125.0</v>
+        <v>1123288.0</v>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
@@ -3123,56 +2953,50 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>453323</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>23/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H41" s="6"/>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K41" s="13" t="n">
-        <v>1388889.0</v>
+        <v>1684932.0</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>111111.0</v>
-      </c>
-      <c r="M41" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M41" s="13"/>
       <c r="N41" s="13"/>
       <c r="O41" s="13" t="n">
-        <v>1500000.0</v>
+        <v>1684932.0</v>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
@@ -3206,56 +3030,50 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TVT</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>454970</t>
+          <t>33725</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>1400116233</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN THỊNH VƯỢNG VÀ PHÁT TRIỂN</t>
+        </is>
+      </c>
+      <c r="H42" s="6"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CTY TNHH DAI PHU HIEP</t>
         </is>
       </c>
       <c r="K42" s="13" t="n">
-        <v>462963.0</v>
+        <v>23000.0</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M42" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>2300.0</v>
+      </c>
+      <c r="M42" s="13"/>
       <c r="N42" s="13"/>
       <c r="O42" s="13" t="n">
-        <v>500000.0</v>
+        <v>25300.0</v>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
@@ -3289,56 +3107,50 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TCC</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>455906</t>
+          <t>474142</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>14/09/2025</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>3500342374</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>TRUNG TÂM NƯỚC SẠCH VÀ VỆ SINH MÔI TRƯỜNG NÔNG THÔN</t>
+        </is>
+      </c>
+      <c r="H43" s="6"/>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K43" s="13" t="n">
-        <v>555556.0</v>
+        <v>160800.0</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>44444.0</v>
-      </c>
-      <c r="M43" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>8040.0</v>
+      </c>
+      <c r="M43" s="13"/>
       <c r="N43" s="13"/>
       <c r="O43" s="13" t="n">
-        <v>600000.0</v>
+        <v>168840.0</v>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
@@ -3372,56 +3184,50 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TCC</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>459140</t>
+          <t>507588</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>3500342374</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>TRUNG TÂM NƯỚC SẠCH VÀ VỆ SINH MÔI TRƯỜNG NÔNG THÔN</t>
+        </is>
+      </c>
+      <c r="H44" s="6"/>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K44" s="13" t="n">
-        <v>462963.0</v>
+        <v>670000.0</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M44" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>33500.0</v>
+      </c>
+      <c r="M44" s="13"/>
       <c r="N44" s="13"/>
       <c r="O44" s="13" t="n">
-        <v>500000.0</v>
+        <v>703500.0</v>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
@@ -3455,56 +3261,52 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TPM</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>461225</t>
+          <t>250535</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>28/09/2025</t>
+          <t>17/09/2025</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>3500677525</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC PHÚ MỸ</t>
+        </is>
+      </c>
+      <c r="H45" s="6"/>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K45" s="13" t="n">
-        <v>555556.0</v>
+        <v>294800.0</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>44444.0</v>
-      </c>
-      <c r="M45" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N45" s="13"/>
+        <v>14740.0</v>
+      </c>
+      <c r="M45" s="13"/>
+      <c r="N45" s="13" t="n">
+        <v>29480.0</v>
+      </c>
       <c r="O45" s="13" t="n">
-        <v>600000.0</v>
+        <v>339020.0</v>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
@@ -3538,17 +3340,17 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TBC</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>464514</t>
+          <t>267482</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -3568,26 +3370,26 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K46" s="13" t="n">
-        <v>463463.0</v>
+        <v>462963.0</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>37077.0</v>
+        <v>37037.0</v>
       </c>
       <c r="M46" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N46" s="13"/>
       <c r="O46" s="13" t="n">
-        <v>500540.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
@@ -3605,6 +3407,2081 @@
         </is>
       </c>
       <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>K25TBL</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>208529</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>06/09/2025</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>4874028.0</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>389922.0</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13" t="n">
+        <v>5263950.0</v>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q47" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>K25TBL</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>211397</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="n">
+        <v>1026111.0</v>
+      </c>
+      <c r="L48" s="13" t="n">
+        <v>82089.0</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N48" s="13"/>
+      <c r="O48" s="13" t="n">
+        <v>1108200.0</v>
+      </c>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q48" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>K25TBL</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>211399</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="n">
+        <v>5130556.0</v>
+      </c>
+      <c r="L49" s="13" t="n">
+        <v>410444.0</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13" t="n">
+        <v>5541000.0</v>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q49" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>K25TBL</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>213605</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>13/09/2025</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="n">
+        <v>4711778.0</v>
+      </c>
+      <c r="L50" s="13" t="n">
+        <v>376942.0</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13" t="n">
+        <v>5088720.0</v>
+      </c>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q50" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S50" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>K25TBL</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>215877</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="n">
+        <v>1035556.0</v>
+      </c>
+      <c r="L51" s="13" t="n">
+        <v>82844.0</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13" t="n">
+        <v>1118400.0</v>
+      </c>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q51" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S51" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>K25TBL</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>218047</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="n">
+        <v>1558333.0</v>
+      </c>
+      <c r="L52" s="13" t="n">
+        <v>124667.0</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13" t="n">
+        <v>1683000.0</v>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q52" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S52" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>K25TBL</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>220241</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="n">
+        <v>3982407.0</v>
+      </c>
+      <c r="L53" s="13" t="n">
+        <v>318593.0</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13" t="n">
+        <v>4301000.0</v>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q53" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S53" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>K25TBL</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>222791</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="n">
+        <v>1038889.0</v>
+      </c>
+      <c r="L54" s="13" t="n">
+        <v>83111.0</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13" t="n">
+        <v>1122000.0</v>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q54" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S54" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>K25TBL</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>223261</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="n">
+        <v>915231.0</v>
+      </c>
+      <c r="L55" s="13" t="n">
+        <v>73219.0</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13" t="n">
+        <v>988450.0</v>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q55" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S55" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>K25TBL</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>225296</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="n">
+        <v>1036111.0</v>
+      </c>
+      <c r="L56" s="13" t="n">
+        <v>82889.0</v>
+      </c>
+      <c r="M56" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13" t="n">
+        <v>1119000.0</v>
+      </c>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q56" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S56" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>190774</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="L57" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="M57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N57" s="13"/>
+      <c r="O57" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q57" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>194080</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="n">
+        <v>1388889.0</v>
+      </c>
+      <c r="L58" s="13" t="n">
+        <v>111111.0</v>
+      </c>
+      <c r="M58" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N58" s="13"/>
+      <c r="O58" s="13" t="n">
+        <v>1500000.0</v>
+      </c>
+      <c r="P58" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q58" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>194507</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>13/09/2025</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>1388889.0</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>111111.0</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N59" s="13"/>
+      <c r="O59" s="13" t="n">
+        <v>1500000.0</v>
+      </c>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q59" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>197179</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L60" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M60" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P60" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q60" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S60" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>197338</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="n">
+        <v>277778.0</v>
+      </c>
+      <c r="L61" s="13" t="n">
+        <v>22222.0</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q61" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S61" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>197339</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>185185.0</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>14815.0</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q62" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S62" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>197340</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N63" s="13"/>
+      <c r="O63" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P63" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q63" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S63" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>197431</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N64" s="13"/>
+      <c r="O64" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q64" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S64" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>197697</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>5177778.0</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>414222.0</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N65" s="13"/>
+      <c r="O65" s="13" t="n">
+        <v>5592000.0</v>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q65" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S65" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>198421</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>1388889.0</v>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>111111.0</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N66" s="13"/>
+      <c r="O66" s="13" t="n">
+        <v>1500000.0</v>
+      </c>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q66" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S66" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>198840</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="n">
+        <v>1388889.0</v>
+      </c>
+      <c r="L67" s="13" t="n">
+        <v>111111.0</v>
+      </c>
+      <c r="M67" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N67" s="13"/>
+      <c r="O67" s="13" t="n">
+        <v>1500000.0</v>
+      </c>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q67" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S67" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>199595</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="n">
+        <v>1388889.0</v>
+      </c>
+      <c r="L68" s="13" t="n">
+        <v>111111.0</v>
+      </c>
+      <c r="M68" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N68" s="13"/>
+      <c r="O68" s="13" t="n">
+        <v>1500000.0</v>
+      </c>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q68" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S68" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>200326</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>21/09/2025</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="L69" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="M69" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N69" s="13"/>
+      <c r="O69" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q69" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S69" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>204906</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>27/09/2025</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L70" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M70" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N70" s="13"/>
+      <c r="O70" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q70" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S70" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>K25TBP</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>206916</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="L71" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="M71" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N71" s="13"/>
+      <c r="O71" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S71" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>
